--- a/MBG01D.xlsx
+++ b/MBG01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="133">
   <si>
     <t/>
   </si>
@@ -79,349 +79,337 @@
     <t>12</t>
   </si>
   <si>
-    <t>20142055</t>
-  </si>
-  <si>
-    <t>TOPI KOKI SETRA RYL5</t>
+    <t>10009392</t>
+  </si>
+  <si>
+    <t>W/A BRS S.SPR KPL 5</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20106876</t>
+  </si>
+  <si>
+    <t>UDG D/KOKI BRS PRM 5</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20097275</t>
+  </si>
+  <si>
+    <t>LAHAP BRS LELE 5KG</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20084982</t>
+  </si>
+  <si>
+    <t>D/KOKI BRAS SHT 5KG</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20142264</t>
+  </si>
+  <si>
+    <t>LAHAP LELE BRS PRM 5</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20128129</t>
+  </si>
+  <si>
+    <t>PUNO/K BERAS 5KG</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20143258</t>
+  </si>
+  <si>
+    <t>SI GEULIS BERAS5KG</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20142056</t>
+  </si>
+  <si>
+    <t>NASIKU/B BERAS PRM 5</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20139555</t>
+  </si>
+  <si>
+    <t>PNKWN BERAS PRMIUM10</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>20143145</t>
+  </si>
+  <si>
+    <t>LHP LELE PREM 10 KG</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20127565</t>
+  </si>
+  <si>
+    <t>S/W BERAS PREMIUM5KG</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20128415</t>
+  </si>
+  <si>
+    <t>MED/SPHP BERAS 5KG</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20002897</t>
+  </si>
+  <si>
+    <t>IDM PANDAN WANGI 5KG</t>
+  </si>
+  <si>
+    <t>20141056</t>
+  </si>
+  <si>
+    <t>SINTANUR PND WGI 5KG</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20142006</t>
+  </si>
+  <si>
+    <t>PTRI KOKI BRS KH 5KG</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20133809</t>
+  </si>
+  <si>
+    <t>DM NASI JAGUNG 250</t>
+  </si>
+  <si>
+    <t>20133810</t>
+  </si>
+  <si>
+    <t>DM NASI SINGKONG 250</t>
+  </si>
+  <si>
+    <t>20140704</t>
+  </si>
+  <si>
+    <t>IDM BRS PORANG 4X40G</t>
+  </si>
+  <si>
+    <t>20088559</t>
+  </si>
+  <si>
+    <t>IDM KETAN PUTIH 500G</t>
+  </si>
+  <si>
+    <t>20088561</t>
+  </si>
+  <si>
+    <t>IDM KETAN HITAM 500G</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20054184</t>
+  </si>
+  <si>
+    <t>IDM BERAS MERAH 2KG</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20141277</t>
+  </si>
+  <si>
+    <t>LARST BRS SLP SPR2.5</t>
+  </si>
+  <si>
+    <t>20134672</t>
+  </si>
+  <si>
+    <t>LRSST GL.KRSTAL 100S</t>
+  </si>
+  <si>
+    <t>TG,(E-1B)</t>
+  </si>
+  <si>
+    <t>20085279</t>
+  </si>
+  <si>
+    <t>IDM GULA PSR STK 30S</t>
+  </si>
+  <si>
+    <t>20085280</t>
+  </si>
+  <si>
+    <t>IDM GULA ARN STK 20S</t>
+  </si>
+  <si>
+    <t>20069092</t>
+  </si>
+  <si>
+    <t>IDM GULA BATU 225</t>
+  </si>
+  <si>
+    <t>20103654</t>
+  </si>
+  <si>
+    <t>IDM GL.AREN (KW) 200</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20121086</t>
+  </si>
+  <si>
+    <t>SUS GULA LKL KNG 1KG</t>
+  </si>
+  <si>
+    <t>TG,(E-2B)</t>
+  </si>
+  <si>
+    <t>20113564</t>
+  </si>
+  <si>
+    <t>GULAVIT GULA KRSTL 1</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>10021008</t>
+  </si>
+  <si>
+    <t>GULAKU GULA KUNG 1KG</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10021010</t>
+  </si>
+  <si>
+    <t>GULAKU GULA PUTIH1KG</t>
+  </si>
+  <si>
+    <t>20042991</t>
+  </si>
+  <si>
+    <t>IDM GULA P.P PT 1KG</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20045854</t>
+  </si>
+  <si>
+    <t>PSM GULA PREMIUM 1KG</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20052296</t>
+  </si>
+  <si>
+    <t>IDM GULA PRM KN 1 KG</t>
+  </si>
+  <si>
+    <t>20076765</t>
+  </si>
+  <si>
+    <t>ROSE/B GULA PTH 1KG</t>
+  </si>
+  <si>
+    <t>20076768</t>
+  </si>
+  <si>
+    <t>ROSE/B GULA KNG 1KG</t>
+  </si>
+  <si>
+    <t>20078207</t>
+  </si>
+  <si>
+    <t>GMP GULA PASIR 1KG</t>
+  </si>
+  <si>
+    <t>20139024</t>
+  </si>
+  <si>
+    <t>LRST GULA KRSTL 500</t>
+  </si>
+  <si>
+    <t>20139025</t>
+  </si>
+  <si>
+    <t>LRST GULA KRSTL 1 KG</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20078902</t>
+  </si>
+  <si>
+    <t>INDOSUGAR GULA 1KG</t>
+  </si>
+  <si>
+    <t>20097781</t>
+  </si>
+  <si>
+    <t>KBA GULA KRSTL 1KG</t>
+  </si>
+  <si>
+    <t>20103543</t>
+  </si>
+  <si>
+    <t>FS GULA PASIR PTH1KG</t>
   </si>
   <si>
     <t>13</t>
-  </si>
-  <si>
-    <t>10009392</t>
-  </si>
-  <si>
-    <t>W/A BRS S.SPR KPL 5</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20106876</t>
-  </si>
-  <si>
-    <t>UDG D/KOKI BRS PRM 5</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20097275</t>
-  </si>
-  <si>
-    <t>LAHAP BRS LELE 5KG</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20084982</t>
-  </si>
-  <si>
-    <t>D/KOKI BRAS SHT 5KG</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20142264</t>
-  </si>
-  <si>
-    <t>LAHAP LELE BRS PRM 5</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20128129</t>
-  </si>
-  <si>
-    <t>PUNO/K BERAS 5KG</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20143258</t>
-  </si>
-  <si>
-    <t>SI GEULIS BERAS5KG</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20142056</t>
-  </si>
-  <si>
-    <t>NASIKU/B BERAS PRM 5</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20139555</t>
-  </si>
-  <si>
-    <t>PNKWN BERAS PRMIUM10</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>20143145</t>
-  </si>
-  <si>
-    <t>LHP LELE PREM 10 KG</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20128415</t>
-  </si>
-  <si>
-    <t>MED/SPHP BERAS 5KG</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20139532</t>
-  </si>
-  <si>
-    <t>A/R BRS KHS PLN WG5</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20002897</t>
-  </si>
-  <si>
-    <t>IDM PANDAN WANGI 5KG</t>
-  </si>
-  <si>
-    <t>20141056</t>
-  </si>
-  <si>
-    <t>SINTANUR PND WGI 5KG</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20142107</t>
-  </si>
-  <si>
-    <t>ARN BERAS KHUSUS 5KG</t>
-  </si>
-  <si>
-    <t>20142006</t>
-  </si>
-  <si>
-    <t>PTRI KOKI BRS KH 5KG</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20133809</t>
-  </si>
-  <si>
-    <t>DM NASI JAGUNG 250</t>
-  </si>
-  <si>
-    <t>20133810</t>
-  </si>
-  <si>
-    <t>DM NASI SINGKONG 250</t>
-  </si>
-  <si>
-    <t>20140704</t>
-  </si>
-  <si>
-    <t>IDM BRS PORANG 4X40G</t>
-  </si>
-  <si>
-    <t>20088559</t>
-  </si>
-  <si>
-    <t>IDM KETAN PUTIH 500G</t>
-  </si>
-  <si>
-    <t>20088561</t>
-  </si>
-  <si>
-    <t>IDM KETAN HITAM 500G</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20054184</t>
-  </si>
-  <si>
-    <t>IDM BERAS MERAH 2KG</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20141277</t>
-  </si>
-  <si>
-    <t>LARST BRS SLP SPR2.5</t>
-  </si>
-  <si>
-    <t>20134672</t>
-  </si>
-  <si>
-    <t>LRSST GL.KRSTAL 100S</t>
-  </si>
-  <si>
-    <t>TG,(E-1B)</t>
-  </si>
-  <si>
-    <t>20085279</t>
-  </si>
-  <si>
-    <t>IDM GULA PSR STK 30S</t>
-  </si>
-  <si>
-    <t>20085280</t>
-  </si>
-  <si>
-    <t>IDM GULA ARN STK 20S</t>
-  </si>
-  <si>
-    <t>20069092</t>
-  </si>
-  <si>
-    <t>IDM GULA BATU 225</t>
-  </si>
-  <si>
-    <t>20103654</t>
-  </si>
-  <si>
-    <t>IDM GL.AREN (KW) 200</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20121086</t>
-  </si>
-  <si>
-    <t>SUS GULA LKL KNG 1KG</t>
-  </si>
-  <si>
-    <t>TG,(E-2B)</t>
-  </si>
-  <si>
-    <t>20113564</t>
-  </si>
-  <si>
-    <t>GULAVIT GULA KRSTL 1</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>10021008</t>
-  </si>
-  <si>
-    <t>GULAKU GULA KUNG 1KG</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10021010</t>
-  </si>
-  <si>
-    <t>GULAKU GULA PUTIH1KG</t>
-  </si>
-  <si>
-    <t>20042991</t>
-  </si>
-  <si>
-    <t>IDM GULA PSR PRM 1KG</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20045854</t>
-  </si>
-  <si>
-    <t>PSM GULA PREMIUM 1KG</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20052296</t>
-  </si>
-  <si>
-    <t>IDM GULA PRM KNG 1KG</t>
-  </si>
-  <si>
-    <t>20076765</t>
-  </si>
-  <si>
-    <t>ROSE/B GULA PTH 1KG</t>
-  </si>
-  <si>
-    <t>20076768</t>
-  </si>
-  <si>
-    <t>ROSE/B GULA KNG 1KG</t>
-  </si>
-  <si>
-    <t>20078207</t>
-  </si>
-  <si>
-    <t>GMP GULA PASIR 1KG</t>
-  </si>
-  <si>
-    <t>20139024</t>
-  </si>
-  <si>
-    <t>LRST GULA KRSTL 500</t>
-  </si>
-  <si>
-    <t>20139025</t>
-  </si>
-  <si>
-    <t>LRST GULA KRSTL 1KG</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20078902</t>
-  </si>
-  <si>
-    <t>INDOSUGAR GULA 1KG</t>
-  </si>
-  <si>
-    <t>20097781</t>
-  </si>
-  <si>
-    <t>KBA GULA KRSTL 1KG</t>
-  </si>
-  <si>
-    <t>20103543</t>
-  </si>
-  <si>
-    <t>FS GULA PASIR PTH1KG</t>
   </si>
 </sst>
 </file>
@@ -814,7 +802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -982,7 +970,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1002,15 +990,15 @@
         <v>27</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1019,10 +1007,10 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1122,7 +1110,7 @@
         <v>46</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1162,7 +1150,7 @@
         <v>52</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1219,18 +1207,18 @@
         <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1239,7 +1227,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>12</v>
@@ -1276,10 +1264,10 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>12</v>
@@ -1296,10 +1284,10 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>12</v>
@@ -1307,10 +1295,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1319,7 +1307,7 @@
         <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>12</v>
@@ -1327,10 +1315,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1339,18 +1327,18 @@
         <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1359,10 +1347,10 @@
         <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1379,7 +1367,7 @@
         <v>11</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1387,10 +1375,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1399,10 +1387,10 @@
         <v>11</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1416,13 +1404,13 @@
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1436,13 +1424,13 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="F31" s="1" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1456,53 +1444,53 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1516,73 +1504,73 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1599,7 +1587,7 @@
         <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>109</v>
@@ -1619,18 +1607,18 @@
         <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -1639,10 +1627,10 @@
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1662,15 +1650,15 @@
         <v>66</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -1679,18 +1667,18 @@
         <v>15</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -1699,18 +1687,18 @@
         <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>109</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -1719,18 +1707,18 @@
         <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -1739,10 +1727,10 @@
         <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1759,10 +1747,10 @@
         <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>109</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1779,18 +1767,18 @@
         <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>109</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -1799,49 +1787,9 @@
         <v>15</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>18</v>
+        <v>132</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F51" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/MBG01D.xlsx
+++ b/MBG01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="132">
   <si>
     <t/>
   </si>
@@ -85,7 +85,7 @@
     <t>W/A BRS S.SPR KPL 5</t>
   </si>
   <si>
-    <t>14</t>
+    <t>13</t>
   </si>
   <si>
     <t>20106876</t>
@@ -94,93 +94,93 @@
     <t>UDG D/KOKI BRS PRM 5</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20097275</t>
+  </si>
+  <si>
+    <t>LAHAP BRS LELE 5KG</t>
+  </si>
+  <si>
     <t>16</t>
   </si>
   <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20097275</t>
-  </si>
-  <si>
-    <t>LAHAP BRS LELE 5KG</t>
+    <t>20084982</t>
+  </si>
+  <si>
+    <t>D/KOKI BRAS SHT 5KG</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>20084982</t>
-  </si>
-  <si>
-    <t>D/KOKI BRAS SHT 5KG</t>
+    <t>20142264</t>
+  </si>
+  <si>
+    <t>LAHAP LELE BRS PRM 5</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>20142264</t>
-  </si>
-  <si>
-    <t>LAHAP LELE BRS PRM 5</t>
+    <t>20128129</t>
+  </si>
+  <si>
+    <t>PUNO/K BERAS 5KG</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
-    <t>20128129</t>
-  </si>
-  <si>
-    <t>PUNO/K BERAS 5KG</t>
+    <t>20143258</t>
+  </si>
+  <si>
+    <t>SI GEULIS BERAS5KG</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>20143258</t>
-  </si>
-  <si>
-    <t>SI GEULIS BERAS5KG</t>
+    <t>20142056</t>
+  </si>
+  <si>
+    <t>NASIKU/B BERAS PRM 5</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>20142056</t>
-  </si>
-  <si>
-    <t>NASIKU/B BERAS PRM 5</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>20139555</t>
   </si>
   <si>
     <t>PNKWN BERAS PRMIUM10</t>
   </si>
   <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20143145</t>
+  </si>
+  <si>
+    <t>LHP LELE PREM 10 KG</t>
+  </si>
+  <si>
     <t>24</t>
   </si>
   <si>
-    <t>20143145</t>
-  </si>
-  <si>
-    <t>LHP LELE PREM 10 KG</t>
+    <t>20127565</t>
+  </si>
+  <si>
+    <t>S/W BERAS PREMIUM5KG</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>20127565</t>
-  </si>
-  <si>
-    <t>S/W BERAS PREMIUM5KG</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
     <t>20128415</t>
   </si>
   <si>
@@ -313,75 +313,75 @@
     <t>GULAVIT GULA KRSTL 1</t>
   </si>
   <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>10021008</t>
+  </si>
+  <si>
+    <t>GULAKU GULA KUNG 1KG</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10021010</t>
+  </si>
+  <si>
+    <t>GULAKU GULA PUTIH1KG</t>
+  </si>
+  <si>
+    <t>20042991</t>
+  </si>
+  <si>
+    <t>IDM GULA P.P PT 1KG</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20045854</t>
+  </si>
+  <si>
+    <t>PSM GULA PREMIUM 1KG</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20052296</t>
+  </si>
+  <si>
+    <t>IDM GULA PRM KN 1 KG</t>
+  </si>
+  <si>
+    <t>20076765</t>
+  </si>
+  <si>
+    <t>ROSE/B GULA PTH 1KG</t>
+  </si>
+  <si>
+    <t>20076768</t>
+  </si>
+  <si>
+    <t>ROSE/B GULA KNG 1KG</t>
+  </si>
+  <si>
+    <t>20078207</t>
+  </si>
+  <si>
+    <t>GMP GULA PASIR 1KG</t>
+  </si>
+  <si>
+    <t>20139024</t>
+  </si>
+  <si>
+    <t>LRST GULA KRSTL 500</t>
+  </si>
+  <si>
     <t>9</t>
   </si>
   <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>10021008</t>
-  </si>
-  <si>
-    <t>GULAKU GULA KUNG 1KG</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10021010</t>
-  </si>
-  <si>
-    <t>GULAKU GULA PUTIH1KG</t>
-  </si>
-  <si>
-    <t>20042991</t>
-  </si>
-  <si>
-    <t>IDM GULA P.P PT 1KG</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20045854</t>
-  </si>
-  <si>
-    <t>PSM GULA PREMIUM 1KG</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20052296</t>
-  </si>
-  <si>
-    <t>IDM GULA PRM KN 1 KG</t>
-  </si>
-  <si>
-    <t>20076765</t>
-  </si>
-  <si>
-    <t>ROSE/B GULA PTH 1KG</t>
-  </si>
-  <si>
-    <t>20076768</t>
-  </si>
-  <si>
-    <t>ROSE/B GULA KNG 1KG</t>
-  </si>
-  <si>
-    <t>20078207</t>
-  </si>
-  <si>
-    <t>GMP GULA PASIR 1KG</t>
-  </si>
-  <si>
-    <t>20139024</t>
-  </si>
-  <si>
-    <t>LRST GULA KRSTL 500</t>
-  </si>
-  <si>
     <t>20139025</t>
   </si>
   <si>
@@ -407,9 +407,6 @@
   </si>
   <si>
     <t>FS GULA PASIR PTH1KG</t>
-  </si>
-  <si>
-    <t>13</t>
   </si>
 </sst>
 </file>
@@ -1387,7 +1384,7 @@
         <v>11</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>12</v>
@@ -1407,7 +1404,7 @@
         <v>63</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>85</v>
@@ -1427,7 +1424,7 @@
         <v>63</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>58</v>
@@ -1447,7 +1444,7 @@
         <v>63</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>58</v>
@@ -1467,7 +1464,7 @@
         <v>63</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>12</v>
@@ -1487,7 +1484,7 @@
         <v>63</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>94</v>
@@ -1507,7 +1504,7 @@
         <v>63</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>97</v>
@@ -1527,18 +1524,18 @@
         <v>63</v>
       </c>
       <c r="E36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1550,15 +1547,15 @@
         <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -1570,15 +1567,15 @@
         <v>8</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -1590,15 +1587,15 @@
         <v>11</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -1610,15 +1607,15 @@
         <v>63</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -1630,15 +1627,15 @@
         <v>15</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -1650,15 +1647,15 @@
         <v>66</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -1670,15 +1667,15 @@
         <v>77</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -1695,10 +1692,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -1707,10 +1704,10 @@
         <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1730,7 +1727,7 @@
         <v>125</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1787,7 +1784,7 @@
         <v>15</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
